--- a/output/StructureDefinition-RNDSProfissional.xlsx
+++ b/output/StructureDefinition-RNDSProfissional.xlsx
@@ -616,7 +616,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/namingsystem-identifier-system-type</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0203</t>
   </si>
   <si>
     <t>Identifier.type</t>
